--- a/database/template-import-export/templates/template-perikanan.xlsx
+++ b/database/template-import-export/templates/template-perikanan.xlsx
@@ -40,7 +40,7 @@
     <t>Produksi tangkap/budidaya/benih, luas kolam-waduk-minapadi, tempat pemeliharaan, dan obyek penangkapan.</t>
   </si>
   <si>
-    <t>Dibuat otomatis: 22/9/2026, 14.21.32</t>
+    <t>Dibuat otomatis: 29/9/2026, 15.29.42</t>
   </si>
   <si>
     <t>CARA PAKAI</t>
